--- a/Template_Import_Leasing.xlsx
+++ b/Template_Import_Leasing.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Data" sheetId="1" r:id="Read715c7c6d34cfb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Petunjuk" sheetId="2" r:id="R1d90319cbb4140aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contoh — Jangan Import" sheetId="3" r:id="R4076ffa339984f3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panduan Kolom" sheetId="4" r:id="Rbbb02ff2c3194054"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Data" sheetId="1" r:id="Rdd56a2001fb24920"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Petunjuk" sheetId="2" r:id="R99edf72f6ea841c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contoh — Jangan Import" sheetId="3" r:id="Rfb55302bcfb340ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panduan Kolom" sheetId="4" r:id="R9e92a7f1888c4b3e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -135,14 +135,12 @@
   <x:borders count="3">
     <x:border/>
     <x:border/>
-    <x:border>
-      <x:bottom/>
-    </x:border>
+    <x:border/>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="76">
+  <x:cellXfs count="80">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -319,6 +317,18 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -543,7 +553,7 @@
     <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="34" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="13" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="13" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="34" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="13" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="46" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="34" hidden="0" customWidth="1"/>
@@ -558,7 +568,7 @@
     <x:col min="24" max="24" width="16" hidden="0" customWidth="1"/>
     <x:col min="25" max="25" width="34" hidden="0" customWidth="1"/>
     <x:col min="26" max="26" width="18" hidden="0" customWidth="1"/>
-    <x:col min="27" max="27" width="21" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="2" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -596,53 +606,51 @@
         <x:v>Postal Code</x:v>
       </x:c>
       <x:c r="L1" s="6" t="str">
-        <x:v>Latitude</x:v>
+        <x:v>Coordinates (Latitude, Longitude)</x:v>
       </x:c>
       <x:c r="M1" s="6" t="str">
-        <x:v>Longitude</x:v>
+        <x:v>Requested Services</x:v>
       </x:c>
       <x:c r="N1" s="6" t="str">
-        <x:v>Requested Services</x:v>
+        <x:v>Site Notes</x:v>
       </x:c>
       <x:c r="O1" s="6" t="str">
-        <x:v>Site Notes</x:v>
+        <x:v>External Reference</x:v>
       </x:c>
       <x:c r="P1" s="6" t="str">
-        <x:v>External Reference</x:v>
+        <x:v>Order Type</x:v>
       </x:c>
       <x:c r="Q1" s="6" t="str">
-        <x:v>Order Type</x:v>
+        <x:v>SI</x:v>
       </x:c>
       <x:c r="R1" s="6" t="str">
-        <x:v>SI</x:v>
+        <x:v>Area</x:v>
       </x:c>
       <x:c r="S1" s="6" t="str">
-        <x:v>Area</x:v>
+        <x:v>Gedung/Kawasan</x:v>
       </x:c>
       <x:c r="T1" s="6" t="str">
-        <x:v>Gedung/Kawasan</x:v>
+        <x:v>A-End</x:v>
       </x:c>
       <x:c r="U1" s="6" t="str">
-        <x:v>A-End</x:v>
+        <x:v>Z-End</x:v>
       </x:c>
       <x:c r="V1" s="6" t="str">
-        <x:v>Z-End</x:v>
+        <x:v>Bandwidth</x:v>
       </x:c>
       <x:c r="W1" s="6" t="str">
-        <x:v>Bandwidth</x:v>
+        <x:v>Bandwidth Unit</x:v>
       </x:c>
       <x:c r="X1" s="6" t="str">
-        <x:v>Bandwidth Unit</x:v>
+        <x:v>Special Features</x:v>
       </x:c>
       <x:c r="Y1" s="6" t="str">
-        <x:v>Special Features</x:v>
+        <x:v>Existing MRC</x:v>
       </x:c>
       <x:c r="Z1" s="6" t="str">
-        <x:v>Existing MRC</x:v>
-      </x:c>
-      <x:c r="AA1" s="6" t="str">
         <x:v>Existing MRC Currency</x:v>
       </x:c>
+      <x:c r="AA1" s="6"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="12"/>
@@ -67769,12 +67777,12 @@
         <x:v>Customer, Requester, Project Name, Site, Address, Requested Services. Kolom order/routing Non-Project biasanya boleh kosong.</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="43" customHeight="1">
+    <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tanggal dan angka</x:v>
       </x:c>
       <x:c r="B13" s="12" t="str">
-        <x:v>Gunakan tanggal Excel pada kolom Due Date. Latitude -90..90, Longitude -180..180, Bandwidth &gt; 0, Existing MRC tidak boleh negatif.</x:v>
+        <x:v>Gunakan tanggal Excel pada kolom Due Date. Coordinates opsional: satu sel berformat Latitude, Longitude, contoh -6.169524526528727, 106.80415736497478 (latitude dulu; titik untuk desimal). Bandwidth Non-Project wajib &gt; 0; Bandwidth Project opsional, tetapi jika diisi harus &gt; 0. Existing MRC tidak boleh negatif.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="43" customHeight="1">
@@ -67901,7 +67909,7 @@
     <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="34" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="13" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="13" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="34" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="13" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="46" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="34" hidden="0" customWidth="1"/>
@@ -67916,7 +67924,7 @@
     <x:col min="24" max="24" width="16" hidden="0" customWidth="1"/>
     <x:col min="25" max="25" width="34" hidden="0" customWidth="1"/>
     <x:col min="26" max="26" width="18" hidden="0" customWidth="1"/>
-    <x:col min="27" max="27" width="21" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="2" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -67954,53 +67962,51 @@
         <x:v>Postal Code</x:v>
       </x:c>
       <x:c r="L1" s="32" t="str">
-        <x:v>Latitude</x:v>
+        <x:v>Coordinates (Latitude, Longitude)</x:v>
       </x:c>
       <x:c r="M1" s="32" t="str">
-        <x:v>Longitude</x:v>
+        <x:v>Requested Services</x:v>
       </x:c>
       <x:c r="N1" s="32" t="str">
-        <x:v>Requested Services</x:v>
+        <x:v>Site Notes</x:v>
       </x:c>
       <x:c r="O1" s="32" t="str">
-        <x:v>Site Notes</x:v>
+        <x:v>External Reference</x:v>
       </x:c>
       <x:c r="P1" s="32" t="str">
-        <x:v>External Reference</x:v>
+        <x:v>Order Type</x:v>
       </x:c>
       <x:c r="Q1" s="32" t="str">
-        <x:v>Order Type</x:v>
+        <x:v>SI</x:v>
       </x:c>
       <x:c r="R1" s="32" t="str">
-        <x:v>SI</x:v>
+        <x:v>Area</x:v>
       </x:c>
       <x:c r="S1" s="32" t="str">
-        <x:v>Area</x:v>
+        <x:v>Gedung/Kawasan</x:v>
       </x:c>
       <x:c r="T1" s="32" t="str">
-        <x:v>Gedung/Kawasan</x:v>
+        <x:v>A-End</x:v>
       </x:c>
       <x:c r="U1" s="32" t="str">
-        <x:v>A-End</x:v>
+        <x:v>Z-End</x:v>
       </x:c>
       <x:c r="V1" s="32" t="str">
-        <x:v>Z-End</x:v>
+        <x:v>Bandwidth</x:v>
       </x:c>
       <x:c r="W1" s="32" t="str">
-        <x:v>Bandwidth</x:v>
+        <x:v>Bandwidth Unit</x:v>
       </x:c>
       <x:c r="X1" s="32" t="str">
-        <x:v>Bandwidth Unit</x:v>
+        <x:v>Special Features</x:v>
       </x:c>
       <x:c r="Y1" s="32" t="str">
-        <x:v>Special Features</x:v>
+        <x:v>Existing MRC</x:v>
       </x:c>
       <x:c r="Z1" s="32" t="str">
-        <x:v>Existing MRC</x:v>
-      </x:c>
-      <x:c r="AA1" s="32" t="str">
         <x:v>Existing MRC Currency</x:v>
       </x:c>
+      <x:c r="AA1" s="32"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="12" t="str">
@@ -68036,28 +68042,30 @@
       <x:c r="K2" s="12" t="str">
         <x:v>10110</x:v>
       </x:c>
-      <x:c r="L2" s="12" t="n">
-        <x:v>-6.2</x:v>
+      <x:c r="L2" s="12" t="str">
+        <x:v>-6.200000, 106.800000</x:v>
       </x:c>
-      <x:c r="M2" s="12" t="n">
-        <x:v>106.8</x:v>
+      <x:c r="M2" s="12" t="str">
+        <x:v>Managed Connectivity; Cybersecurity; Cloud Backup; IoT Management</x:v>
       </x:c>
       <x:c r="N2" s="12" t="str">
-        <x:v>Managed Connectivity; Cybersecurity; Cloud Backup; IoT Management</x:v>
+        <x:v>Contoh proyek</x:v>
       </x:c>
       <x:c r="O2" s="12" t="str">
-        <x:v>Contoh proyek</x:v>
-      </x:c>
-      <x:c r="P2" s="12" t="str">
         <x:v>SRC-REQ-001</x:v>
       </x:c>
+      <x:c r="P2" s="12"/>
       <x:c r="Q2" s="12"/>
       <x:c r="R2" s="12"/>
       <x:c r="S2" s="12"/>
       <x:c r="T2" s="12"/>
       <x:c r="U2" s="12"/>
-      <x:c r="V2" s="12"/>
-      <x:c r="W2" s="12"/>
+      <x:c r="V2" s="12" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="W2" s="12" t="str">
+        <x:v>Mbps</x:v>
+      </x:c>
       <x:c r="X2" s="12"/>
       <x:c r="Y2" s="12"/>
       <x:c r="Z2" s="12"/>
@@ -68097,28 +68105,30 @@
       <x:c r="K3" s="12" t="str">
         <x:v>10120</x:v>
       </x:c>
-      <x:c r="L3" s="12" t="n">
-        <x:v>-6.21</x:v>
+      <x:c r="L3" s="12" t="str">
+        <x:v>-6.210000, 106.810000</x:v>
       </x:c>
-      <x:c r="M3" s="12" t="n">
-        <x:v>106.81</x:v>
+      <x:c r="M3" s="12" t="str">
+        <x:v>Managed Connectivity; Cybersecurity; Cloud Backup; IoT Management</x:v>
       </x:c>
       <x:c r="N3" s="12" t="str">
-        <x:v>Managed Connectivity; Cybersecurity; Cloud Backup; IoT Management</x:v>
+        <x:v>Contoh proyek</x:v>
       </x:c>
       <x:c r="O3" s="12" t="str">
-        <x:v>Contoh proyek</x:v>
-      </x:c>
-      <x:c r="P3" s="12" t="str">
         <x:v>SRC-REQ-002</x:v>
       </x:c>
+      <x:c r="P3" s="12"/>
       <x:c r="Q3" s="12"/>
       <x:c r="R3" s="12"/>
       <x:c r="S3" s="12"/>
       <x:c r="T3" s="12"/>
       <x:c r="U3" s="12"/>
-      <x:c r="V3" s="12"/>
-      <x:c r="W3" s="12"/>
+      <x:c r="V3" s="12" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="W3" s="12" t="str">
+        <x:v>Mbps</x:v>
+      </x:c>
       <x:c r="X3" s="12"/>
       <x:c r="Y3" s="12"/>
       <x:c r="Z3" s="12"/>
@@ -68152,46 +68162,62 @@
       <x:c r="K4" s="12" t="str">
         <x:v>10220</x:v>
       </x:c>
-      <x:c r="L4" s="12" t="n">
-        <x:v>-6.22</x:v>
+      <x:c r="L4" s="12" t="str">
+        <x:v>-6.220000, 106.820000</x:v>
       </x:c>
-      <x:c r="M4" s="12" t="n">
-        <x:v>106.82</x:v>
-      </x:c>
-      <x:c r="N4" s="12" t="str">
+      <x:c r="M4" s="12" t="str">
         <x:v>Managed Router; Security Service</x:v>
       </x:c>
-      <x:c r="O4" s="12"/>
-      <x:c r="P4" s="12" t="str">
+      <x:c r="N4" s="12"/>
+      <x:c r="O4" s="12" t="str">
         <x:v>SRC-REQ-003</x:v>
       </x:c>
-      <x:c r="Q4" s="12" t="str">
+      <x:c r="P4" s="12" t="str">
         <x:v>PSB</x:v>
       </x:c>
-      <x:c r="R4" s="12"/>
-      <x:c r="S4" s="12" t="str">
+      <x:c r="Q4" s="12"/>
+      <x:c r="R4" s="12" t="str">
         <x:v>Jakarta</x:v>
       </x:c>
-      <x:c r="T4" s="12"/>
-      <x:c r="U4" s="12" t="str">
+      <x:c r="S4" s="12"/>
+      <x:c r="T4" s="12" t="str">
         <x:v>Jakarta</x:v>
       </x:c>
-      <x:c r="V4" s="12"/>
-      <x:c r="W4" s="12" t="n">
+      <x:c r="U4" s="12"/>
+      <x:c r="V4" s="12" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="X4" s="12" t="str">
+      <x:c r="W4" s="12" t="str">
         <x:v>Mbps</x:v>
       </x:c>
-      <x:c r="Y4" s="12" t="str">
+      <x:c r="X4" s="12" t="str">
         <x:v>Tidak ada</x:v>
       </x:c>
-      <x:c r="Z4" s="12" t="n">
+      <x:c r="Y4" s="12" t="n">
         <x:v>1250000</x:v>
       </x:c>
-      <x:c r="AA4" s="12" t="str">
+      <x:c r="Z4" s="12" t="str">
         <x:v>IDR</x:v>
       </x:c>
+      <x:c r="AA4" s="12"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="AA5"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="AA6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="AA7"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="AA8"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="AA9"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="AA10"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -68413,9 +68439,9 @@
         <x:v>Disarankan disimpan sebagai teks agar nol di depan tidak hilang.</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="48" customHeight="1">
+    <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="62" t="str">
-        <x:v>Latitude</x:v>
+        <x:v>Coordinates (Latitude, Longitude)</x:v>
       </x:c>
       <x:c r="B13" s="67" t="str">
         <x:v>Opsional</x:v>
@@ -68427,46 +68453,46 @@
         <x:v>Opsional</x:v>
       </x:c>
       <x:c r="E13" s="63" t="str">
-        <x:v>Jika diisi, angka harus berada antara -90 dan 90. Idealnya isi bersama Longitude.</x:v>
+        <x:v>Isi satu sel dalam format Latitude, Longitude; contoh: -6.169524526528727, 106.80415736497478. Urutan latitude dulu, longitude kedua; gunakan titik untuk desimal dan koma sebagai pemisah. Jika diisi, keduanya harus valid.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="48" customHeight="1">
       <x:c r="A14" s="62" t="str">
-        <x:v>Longitude</x:v>
+        <x:v>Requested Services</x:v>
       </x:c>
       <x:c r="B14" s="67" t="str">
+        <x:v>WAJIB</x:v>
+      </x:c>
+      <x:c r="C14" s="67" t="str">
+        <x:v>WAJIB</x:v>
+      </x:c>
+      <x:c r="D14" s="63" t="str">
+        <x:v>Wajib</x:v>
+      </x:c>
+      <x:c r="E14" s="63" t="str">
+        <x:v>Nama jasa bebas, tidak terbatas pada katalog tertentu. Pisahkan lebih dari satu jasa dengan titik koma (;). Jangan mengasumsikan harga wajib ada saat intake.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="48" customHeight="1">
+      <x:c r="A15" s="62" t="str">
+        <x:v>Site Notes</x:v>
+      </x:c>
+      <x:c r="B15" s="69" t="str">
         <x:v>Opsional</x:v>
       </x:c>
-      <x:c r="C14" s="67" t="str">
+      <x:c r="C15" s="69" t="str">
         <x:v>Opsional</x:v>
       </x:c>
-      <x:c r="D14" s="63" t="str">
+      <x:c r="D15" s="63" t="str">
         <x:v>Opsional</x:v>
       </x:c>
-      <x:c r="E14" s="63" t="str">
-        <x:v>Jika diisi, angka harus berada antara -180 dan 180. Idealnya isi bersama Latitude.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="48" customHeight="1">
-      <x:c r="A15" s="62" t="str">
-        <x:v>Requested Services</x:v>
-      </x:c>
-      <x:c r="B15" s="69" t="str">
-        <x:v>WAJIB</x:v>
-      </x:c>
-      <x:c r="C15" s="69" t="str">
-        <x:v>WAJIB</x:v>
-      </x:c>
-      <x:c r="D15" s="63" t="str">
-        <x:v>Wajib</x:v>
-      </x:c>
       <x:c r="E15" s="63" t="str">
-        <x:v>Nama jasa bebas, tidak terbatas pada katalog tertentu. Pisahkan lebih dari satu jasa dengan titik koma (;). Jangan mengasumsikan harga wajib ada saat intake.</x:v>
+        <x:v>Catatan khusus per site/requirement, bukan catatan umum Work Item.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="48" customHeight="1">
       <x:c r="A16" s="62" t="str">
-        <x:v>Site Notes</x:v>
+        <x:v>External Reference</x:v>
       </x:c>
       <x:c r="B16" s="67" t="str">
         <x:v>Opsional</x:v>
@@ -68478,212 +68504,202 @@
         <x:v>Opsional</x:v>
       </x:c>
       <x:c r="E16" s="63" t="str">
-        <x:v>Catatan khusus per site/requirement, bukan catatan umum Work Item.</x:v>
+        <x:v>ID sumber/per-request asli. Berguna ketika beberapa request sumber digabung menjadi satu Work Item.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
       <x:c r="A17" s="62" t="str">
-        <x:v>External Reference</x:v>
+        <x:v>Order Type</x:v>
       </x:c>
       <x:c r="B17" s="67" t="str">
-        <x:v>Opsional</x:v>
+        <x:v>Biarkan kosong</x:v>
       </x:c>
       <x:c r="C17" s="67" t="str">
-        <x:v>Opsional</x:v>
+        <x:v>WAJIB</x:v>
       </x:c>
       <x:c r="D17" s="63" t="str">
-        <x:v>Opsional</x:v>
+        <x:v>Wajib bersyarat</x:v>
       </x:c>
       <x:c r="E17" s="63" t="str">
-        <x:v>ID sumber/per-request asli. Berguna ketika beberapa request sumber digabung menjadi satu Work Item.</x:v>
+        <x:v>Untuk Non-Project: PSB, Relokasi, Upgrade, Downgrade, Change Mitra, atau Change Service.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="48" customHeight="1">
       <x:c r="A18" s="62" t="str">
-        <x:v>Order Type</x:v>
+        <x:v>SI</x:v>
       </x:c>
       <x:c r="B18" s="71" t="str">
         <x:v>Biarkan kosong</x:v>
       </x:c>
       <x:c r="C18" s="69" t="str">
-        <x:v>WAJIB</x:v>
+        <x:v>WAJIB kecuali Order Type = PSB</x:v>
       </x:c>
       <x:c r="D18" s="63" t="str">
         <x:v>Wajib bersyarat</x:v>
       </x:c>
       <x:c r="E18" s="63" t="str">
-        <x:v>Untuk Non-Project: PSB, Relokasi, Upgrade, Downgrade, Change Mitra, atau Change Service.</x:v>
+        <x:v>Service ID boleh kosong untuk PSB (Pasang Baru). Untuk order Non-Project selain PSB, SI wajib.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="48" customHeight="1">
       <x:c r="A19" s="62" t="str">
-        <x:v>SI</x:v>
+        <x:v>Area</x:v>
       </x:c>
       <x:c r="B19" s="71" t="str">
-        <x:v>Biarkan kosong</x:v>
+        <x:v>Opsional (Zone/Area)</x:v>
       </x:c>
       <x:c r="C19" s="69" t="str">
-        <x:v>WAJIB kecuali Order Type = PSB</x:v>
+        <x:v>WAJIB</x:v>
       </x:c>
       <x:c r="D19" s="63" t="str">
         <x:v>Wajib bersyarat</x:v>
       </x:c>
       <x:c r="E19" s="63" t="str">
-        <x:v>Service ID boleh kosong untuk PSB (Pasang Baru). Untuk order Non-Project selain PSB, SI wajib.</x:v>
+        <x:v>Untuk Non-Project wajib diisi. Pada Project, Area dapat diisi melalui Zone atau Area.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="48" customHeight="1">
       <x:c r="A20" s="62" t="str">
-        <x:v>Area</x:v>
+        <x:v>Gedung/Kawasan</x:v>
       </x:c>
       <x:c r="B20" s="67" t="str">
-        <x:v>Opsional (Zone/Area)</x:v>
+        <x:v>Opsional</x:v>
       </x:c>
       <x:c r="C20" s="69" t="str">
+        <x:v>Opsional</x:v>
+      </x:c>
+      <x:c r="D20" s="63" t="str">
+        <x:v>Opsional</x:v>
+      </x:c>
+      <x:c r="E20" s="63" t="str">
+        <x:v>Isi jika site berada dalam gedung/kawasan tertentu.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="48" customHeight="1">
+      <x:c r="A21" s="62" t="str">
+        <x:v>A-End</x:v>
+      </x:c>
+      <x:c r="B21" s="67" t="str">
+        <x:v>Biarkan kosong</x:v>
+      </x:c>
+      <x:c r="C21" s="67" t="str">
         <x:v>WAJIB</x:v>
       </x:c>
-      <x:c r="D20" s="63" t="str">
+      <x:c r="D21" s="63" t="str">
         <x:v>Wajib bersyarat</x:v>
       </x:c>
-      <x:c r="E20" s="63" t="str">
-        <x:v>Untuk Non-Project wajib diisi. Pada Project, Area dapat diisi melalui Zone atau Area.</x:v>
+      <x:c r="E21" s="63" t="str">
+        <x:v>Lokasi atau endpoint A untuk request Non-Project.</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="48" customHeight="1">
-      <x:c r="A21" s="62" t="str">
-        <x:v>Gedung/Kawasan</x:v>
+    <x:row r="22" ht="48" customHeight="1">
+      <x:c r="A22" s="62" t="str">
+        <x:v>Z-End</x:v>
       </x:c>
-      <x:c r="B21" s="67" t="str">
+      <x:c r="B22" s="71" t="str">
         <x:v>Opsional</x:v>
       </x:c>
-      <x:c r="C21" s="67" t="str">
+      <x:c r="C22" s="69" t="str">
         <x:v>Opsional</x:v>
       </x:c>
-      <x:c r="D21" s="63" t="str">
+      <x:c r="D22" s="63" t="str">
         <x:v>Opsional</x:v>
       </x:c>
-      <x:c r="E21" s="63" t="str">
-        <x:v>Isi jika site berada dalam gedung/kawasan tertentu.</x:v>
+      <x:c r="E22" s="63" t="str">
+        <x:v>Endpoint Z jika tersedia.</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="48" customHeight="1">
-      <x:c r="A22" s="62" t="str">
-        <x:v>A-End</x:v>
+    <x:row r="23" ht="44" customHeight="1">
+      <x:c r="A23" s="62" t="str">
+        <x:v>Bandwidth</x:v>
       </x:c>
-      <x:c r="B22" s="71" t="str">
-        <x:v>Biarkan kosong</x:v>
+      <x:c r="B23" s="67" t="str">
+        <x:v>Opsional; jika diisi &gt; 0</x:v>
       </x:c>
-      <x:c r="C22" s="69" t="str">
+      <x:c r="C23" s="67" t="str">
+        <x:v>WAJIB (&gt; 0)</x:v>
+      </x:c>
+      <x:c r="D23" s="63" t="str">
+        <x:v>Wajib bersyarat</x:v>
+      </x:c>
+      <x:c r="E23" s="63" t="str">
+        <x:v>Project dapat menyimpan kapasitas bandwidth per site jika diketahui. Jika diisi harus angka &gt; 0; jika belum diketahui boleh kosong. Non-Project wajib mengisi bandwidth &gt; 0.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="44" customHeight="1">
+      <x:c r="A24" s="62" t="str">
+        <x:v>Bandwidth Unit</x:v>
+      </x:c>
+      <x:c r="B24" s="71" t="str">
+        <x:v>Opsional; default Mbps</x:v>
+      </x:c>
+      <x:c r="C24" s="69" t="str">
+        <x:v>Opsional; default Mbps</x:v>
+      </x:c>
+      <x:c r="D24" s="63" t="str">
+        <x:v>Opsional</x:v>
+      </x:c>
+      <x:c r="E24" s="63" t="str">
+        <x:v>Pilihan: Mbps, Gbps, Kbps, Other. Jika kosong, aplikasi memakai Mbps. Untuk Project, unit hanya relevan bila Bandwidth diisi.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="48" customHeight="1">
+      <x:c r="A25" s="62" t="str">
+        <x:v>Special Features</x:v>
+      </x:c>
+      <x:c r="B25" s="71" t="str">
+        <x:v>Opsional</x:v>
+      </x:c>
+      <x:c r="C25" s="67" t="str">
         <x:v>WAJIB</x:v>
       </x:c>
-      <x:c r="D22" s="63" t="str">
+      <x:c r="D25" s="63" t="str">
         <x:v>Wajib bersyarat</x:v>
       </x:c>
-      <x:c r="E22" s="63" t="str">
-        <x:v>Lokasi atau endpoint A untuk request Non-Project.</x:v>
+      <x:c r="E25" s="63" t="str">
+        <x:v>Deskripsikan kebutuhan khusus untuk Non-Project. Untuk Project boleh kosong.</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="48" customHeight="1">
-      <x:c r="A23" s="62" t="str">
-        <x:v>Z-End</x:v>
+    <x:row r="26" ht="48" customHeight="1">
+      <x:c r="A26" s="62" t="str">
+        <x:v>Existing MRC</x:v>
       </x:c>
-      <x:c r="B23" s="67" t="str">
+      <x:c r="B26" s="67" t="str">
+        <x:v>BIARKAN KOSONG</x:v>
+      </x:c>
+      <x:c r="C26" s="69" t="str">
         <x:v>Opsional</x:v>
       </x:c>
-      <x:c r="C23" s="67" t="str">
-        <x:v>Opsional</x:v>
-      </x:c>
-      <x:c r="D23" s="63" t="str">
-        <x:v>Opsional</x:v>
-      </x:c>
-      <x:c r="E23" s="63" t="str">
-        <x:v>Endpoint Z jika tersedia.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="48" customHeight="1">
-      <x:c r="A24" s="62" t="str">
-        <x:v>Bandwidth</x:v>
-      </x:c>
-      <x:c r="B24" s="71" t="str">
-        <x:v>Biarkan kosong</x:v>
-      </x:c>
-      <x:c r="C24" s="69" t="str">
-        <x:v>WAJIB (&gt; 0)</x:v>
-      </x:c>
-      <x:c r="D24" s="63" t="str">
-        <x:v>Wajib bersyarat</x:v>
-      </x:c>
-      <x:c r="E24" s="63" t="str">
-        <x:v>Bandwidth harus angka lebih besar dari nol. Tidak digunakan pada intake Project.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="48" customHeight="1">
-      <x:c r="A25" s="62" t="str">
-        <x:v>Bandwidth Unit</x:v>
-      </x:c>
-      <x:c r="B25" s="71" t="str">
-        <x:v>Biarkan kosong</x:v>
-      </x:c>
-      <x:c r="C25" s="67" t="str">
-        <x:v>Opsional; default Mbps</x:v>
-      </x:c>
-      <x:c r="D25" s="63" t="str">
-        <x:v>Opsional</x:v>
-      </x:c>
-      <x:c r="E25" s="63" t="str">
-        <x:v>Pilihan: Mbps, Gbps, Kbps, Other. Jika kosong pada Non-Project, aplikasi menggunakan Mbps.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="48" customHeight="1">
-      <x:c r="A26" s="62" t="str">
-        <x:v>Special Features</x:v>
-      </x:c>
-      <x:c r="B26" s="67" t="str">
-        <x:v>Opsional</x:v>
-      </x:c>
-      <x:c r="C26" s="69" t="str">
-        <x:v>WAJIB</x:v>
-      </x:c>
       <x:c r="D26" s="63" t="str">
-        <x:v>Wajib bersyarat</x:v>
+        <x:v>Opsional bersyarat</x:v>
       </x:c>
       <x:c r="E26" s="63" t="str">
-        <x:v>Deskripsikan kebutuhan khusus untuk Non-Project. Untuk Project boleh kosong.</x:v>
+        <x:v>Nilai MRC eksisting harus nol atau lebih. Tidak boleh diisi pada intake Project; target komersial Project diatur terpisah di aplikasi.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="48" customHeight="1">
       <x:c r="A27" s="62" t="str">
-        <x:v>Existing MRC</x:v>
+        <x:v>Existing MRC Currency</x:v>
       </x:c>
       <x:c r="B27" s="71" t="str">
         <x:v>BIARKAN KOSONG</x:v>
       </x:c>
       <x:c r="C27" s="67" t="str">
-        <x:v>Opsional</x:v>
+        <x:v>Opsional; default IDR jika nominal diisi</x:v>
       </x:c>
       <x:c r="D27" s="63" t="str">
         <x:v>Opsional bersyarat</x:v>
       </x:c>
       <x:c r="E27" s="63" t="str">
-        <x:v>Nilai MRC eksisting harus nol atau lebih. Tidak boleh diisi pada intake Project; target komersial Project diatur terpisah di aplikasi.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="48" customHeight="1">
-      <x:c r="A28" s="64" t="str">
-        <x:v>Existing MRC Currency</x:v>
-      </x:c>
-      <x:c r="B28" s="73" t="str">
-        <x:v>BIARKAN KOSONG</x:v>
-      </x:c>
-      <x:c r="C28" s="75" t="str">
-        <x:v>Opsional; default IDR jika nominal diisi</x:v>
-      </x:c>
-      <x:c r="D28" s="65" t="str">
-        <x:v>Opsional bersyarat</x:v>
-      </x:c>
-      <x:c r="E28" s="65" t="str">
         <x:v>Jika diisi, gunakan kode mata uang 3 huruf (contoh IDR, USD). Jangan masukkan simbol mata uang ke nama kolom.</x:v>
       </x:c>
+    </x:row>
+    <x:row r="28" ht="48" customHeight="1">
+      <x:c r="A28" s="64"/>
+      <x:c r="B28" s="73"/>
+      <x:c r="C28" s="75"/>
+      <x:c r="D28" s="65"/>
+      <x:c r="E28" s="65"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
